--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_196_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_196_R20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.008</v>
+        <v>1.786</v>
       </c>
       <c r="E2" t="n">
-        <v>4.718</v>
+        <v>1.2436</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.71</v>
+        <v>0.5423</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0333</v>
+        <v>0.3459</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0767</v>
+        <v>1.2195</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0435</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6078</v>
+        <v>2.2301</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1427</v>
+        <v>2.6286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.465</v>
+        <v>-0.3984</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.641</v>
+        <v>-1.8842</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2195</v>
+        <v>-1.4091</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4216</v>
+        <v>-0.4751</v>
       </c>
       <c r="P2" t="n">
         <v>1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7217</v>
+        <v>0.0483</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1102</v>
+        <v>0.1733</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6115</v>
+        <v>-0.125</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4359</v>
+        <v>1.6623</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.7043</v>
+        <v>2.7756</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1402</v>
+        <v>-1.1133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0359</v>
+        <v>-0.0333</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8198</v>
+        <v>0.0435</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2612</v>
+        <v>1.6078</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7191</v>
+        <v>1.1427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.465</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2252</v>
+        <v>-1.641</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.2195</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1605</v>
+        <v>-0.4216</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2469</v>
+        <v>1.3761</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8057</v>
+        <v>1.1679</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5588</v>
+        <v>0.2082</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6468</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6468</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3921</v>
+        <v>0.6545</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1166</v>
+        <v>1.0376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5087</v>
+        <v>-0.3832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3459</v>
+        <v>-0.8447</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2195</v>
+        <v>-0.3228</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.5219</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2301</v>
+        <v>0.1776</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6286</v>
+        <v>0.0672</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3984</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8842</v>
+        <v>-1.0223</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4091</v>
+        <v>-0.39</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4751</v>
+        <v>-0.6323</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3456</v>
+        <v>0.0147</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.187</v>
+        <v>-0.2122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1586</v>
+        <v>0.2269</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3626</v>
+        <v>0.6101</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5777</v>
+        <v>-0.8712</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2151</v>
+        <v>1.4813</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8447</v>
+        <v>-1.2394</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3228</v>
+        <v>1.066</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5219</v>
+        <v>-2.3054</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1776</v>
+        <v>-1.5897</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0672</v>
+        <v>0.6589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1104</v>
+        <v>-2.2486</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0223</v>
+        <v>0.3503</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.39</v>
+        <v>0.4071</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6323</v>
+        <v>-0.0568</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2772</v>
+        <v>-0.3824</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.3536</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3949</v>
+        <v>-0.0288</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1241</v>
+        <v>0.5688</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2564</v>
+        <v>-1.437</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3805</v>
+        <v>2.0057</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2394</v>
+        <v>0.0359</v>
       </c>
       <c r="H6" t="n">
-        <v>1.066</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3054</v>
+        <v>0.8198</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5897</v>
+        <v>0.2612</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6589</v>
+        <v>-0.7191</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2486</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3503</v>
+        <v>-0.2252</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4071</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0568</v>
+        <v>-0.1605</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8685</v>
+        <v>-0.114</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7389</v>
+        <v>-0.5384</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1296</v>
+        <v>0.4244</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0.6468</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0577</v>
+        <v>0.185</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9153</v>
+        <v>-0.8406</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8575</v>
+        <v>1.0256</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5024</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5759</v>
+        <v>-0.3332</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2161</v>
+        <v>-0.1415</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V7" t="n">
         <v>0.7886</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4083</v>
+        <v>-2.3029</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6853</v>
+        <v>0.5555</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0936</v>
+        <v>-2.8584</v>
       </c>
       <c r="G8" t="n">
         <v>0.1246</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3615</v>
+        <v>0.467</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8338</v>
+        <v>0.704</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V8" t="n">
         <v>-3.3584</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5963</v>
+        <v>-2.6342</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9141</v>
+        <v>-1.8513</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6822</v>
+        <v>-0.783</v>
       </c>
       <c r="G9" t="n">
         <v>0.329</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3738</v>
+        <v>-0.4118</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4007</v>
+        <v>-0.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0268</v>
+        <v>-0.074</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8402</v>
+        <v>-2.6678</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6651</v>
+        <v>-2.7031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8249</v>
+        <v>0.0353</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9244</v>
+        <v>-4.7776</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8571</v>
+        <v>-0.9062</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0673</v>
+        <v>-3.8714</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6129</v>
+        <v>-3.5226</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9173</v>
+        <v>0.1883</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3044</v>
+        <v>-3.7109</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3115</v>
+        <v>-1.2551</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0602</v>
+        <v>-1.0945</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3717</v>
+        <v>-0.1605</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.749</v>
+        <v>-0.1375</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4683</v>
+        <v>0.2833</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2807</v>
+        <v>-0.4208</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0412</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0412</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4149</v>
+        <v>-4.4172</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1814</v>
+        <v>-5.0741</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2336</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7776</v>
+        <v>-1.9244</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9062</v>
+        <v>-0.8571</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8714</v>
+        <v>-1.0673</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.5226</v>
+        <v>-0.6129</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1883</v>
+        <v>-0.9173</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.7109</v>
+        <v>0.3044</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2551</v>
+        <v>-1.3115</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0945</v>
+        <v>0.0602</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1605</v>
+        <v>-1.3717</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8846</v>
+        <v>0.172</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1949</v>
+        <v>0.0593</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6897</v>
+        <v>0.1127</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>-1.0412</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>-1.0412</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6935</v>
+        <v>-4.519</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4333</v>
+        <v>-3.4269</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2601</v>
+        <v>-1.0921</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3628</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6348</v>
+        <v>0.5397</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5895</v>
+        <v>0.4169</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.6882</v>
+        <v>-11.0744</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.2055</v>
+        <v>-10.5919</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4827999999999997</v>
+        <v>-0.483</v>
       </c>
       <c r="G13" t="n">
         <v>-10.8492</v>
@@ -1441,25 +1441,25 @@
         <v>-4.450299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6073000000000004</v>
+        <v>-0.6072999999999997</v>
       </c>
       <c r="K13" t="n">
         <v>-1.4427</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8353999999999995</v>
+        <v>0.8353999999999997</v>
       </c>
       <c r="M13" t="n">
         <v>-10.2418</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.955900000000001</v>
+        <v>-4.9559</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.285799999999999</v>
+        <v>-5.2858</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3195</v>
+        <v>2.319500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.9173</v>
@@ -1468,13 +1468,13 @@
         <v>16.2368</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3751</v>
+        <v>1.2389</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3926</v>
+        <v>1.2212</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01759999999999997</v>
+        <v>0.01759999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.7839</v>
@@ -1483,13 +1483,13 @@
         <v>2.7115</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.495400000000002</v>
+        <v>-6.4954</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3315</v>
+        <v>7.5115</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7855</v>
+        <v>5.1272</v>
       </c>
       <c r="F14" t="n">
-        <v>0.546</v>
+        <v>2.3843</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1548</v>
+        <v>6.3203</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2521</v>
+        <v>1.4753</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0974</v>
+        <v>4.8449</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0982</v>
+        <v>5.584</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8773</v>
+        <v>0.6288</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2208</v>
+        <v>4.9552</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9434</v>
+        <v>0.7363</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3748</v>
+        <v>0.8466</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3182</v>
+        <v>-0.1103</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8726</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4708</v>
+        <v>-0.1373</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4018</v>
+        <v>0.8646</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1024</v>
+        <v>4.828</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3015</v>
+        <v>4.606</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8009</v>
+        <v>0.222</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3203</v>
+        <v>0.1548</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4753</v>
+        <v>1.2521</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8449</v>
+        <v>-1.0974</v>
       </c>
       <c r="J15" t="n">
-        <v>5.584</v>
+        <v>1.0982</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6288</v>
+        <v>0.8773</v>
       </c>
       <c r="L15" t="n">
-        <v>4.9552</v>
+        <v>0.2208</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7363</v>
+        <v>-0.9434</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8466</v>
+        <v>0.3748</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1103</v>
+        <v>-1.3182</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6818</v>
+        <v>1.3691</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>0.2912</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2812</v>
+        <v>1.0778</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8015</v>
+        <v>4.5053</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0931</v>
+        <v>2.2675</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7084</v>
+        <v>2.2379</v>
       </c>
       <c r="G16" t="n">
         <v>5.9435</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8011</v>
+        <v>0.505</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2819</v>
+        <v>0.4562</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5193</v>
+        <v>0.0488</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4145</v>
+        <v>4.23</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0731</v>
+        <v>1.191</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3414</v>
+        <v>3.039</v>
       </c>
       <c r="G17" t="n">
         <v>1.2127</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8949</v>
+        <v>0.5924</v>
       </c>
       <c r="V17" t="n">
         <v>1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7206</v>
+        <v>2.2133</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8388</v>
+        <v>-1.1311</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5594</v>
+        <v>3.3444</v>
       </c>
       <c r="G18" t="n">
         <v>0.9455</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9208</v>
+        <v>0.572</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8883</v>
+        <v>-0.1806</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0325</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.412</v>
+        <v>0.6284</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7245</v>
+        <v>0.0727</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3124</v>
+        <v>0.5556</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1883</v>
+        <v>3.0432</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5029</v>
+        <v>2.0527</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3145</v>
+        <v>0.9905</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0336</v>
+        <v>3.397</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>2.4535</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.222</v>
+        <v>-0.3538</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5365</v>
+        <v>-0.4008</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>0.047</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7038</v>
+        <v>-0.6262</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>-0.2161</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5544</v>
+        <v>-0.4101</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>-1.3247</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3931</v>
+        <v>0.53</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0727</v>
+        <v>0.8424</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3204</v>
+        <v>-0.3124</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0432</v>
+        <v>-0.1883</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0527</v>
+        <v>-0.5029</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9905</v>
+        <v>0.3145</v>
       </c>
       <c r="J20" t="n">
-        <v>3.397</v>
+        <v>0.0336</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4535</v>
+        <v>0.0336</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3538</v>
+        <v>-0.222</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4008</v>
+        <v>-0.5365</v>
       </c>
       <c r="O20" t="n">
-        <v>0.047</v>
+        <v>0.3145</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8615</v>
+        <v>-0.5858</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6453</v>
+        <v>-0.5544</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3247</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1265</v>
+        <v>0.1287</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8079</v>
+        <v>-0.5871</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9344</v>
+        <v>0.7158</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9724</v>
+        <v>1.5769</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2663</v>
+        <v>1.443</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7060999999999999</v>
+        <v>0.1339</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6186</v>
+        <v>1.5734</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6519</v>
+        <v>1.6973</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0333</v>
+        <v>-0.1239</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3538</v>
+        <v>0.0035</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3856</v>
+        <v>-0.2543</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.2578</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9366</v>
+        <v>-0.1957</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7591</v>
+        <v>0.0198</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1775</v>
+        <v>-0.2155</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3943</v>
+        <v>-0.7886</v>
       </c>
       <c r="W21" t="n">
         <v>-0.7886</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4097</v>
+        <v>-0.065</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.823</v>
+        <v>-2.5156</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4133</v>
+        <v>2.4506</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5769</v>
+        <v>-0.9724</v>
       </c>
       <c r="H22" t="n">
-        <v>1.443</v>
+        <v>-0.2663</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1339</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5734</v>
+        <v>-0.6186</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6973</v>
+        <v>-0.6519</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1239</v>
+        <v>0.0333</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0035</v>
+        <v>-0.3538</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2543</v>
+        <v>0.3856</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2578</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7341</v>
+        <v>0.7451</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2161</v>
+        <v>0.0514</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5179</v>
+        <v>0.6937</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7886</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
         <v>-0.7886</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1829</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9621</v>
+        <v>-3.7769</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0218</v>
+        <v>-2.9039</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9402</v>
+        <v>-0.873</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3031</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8909</v>
+        <v>-0.7057</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7494</v>
+        <v>-0.6822</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2421</v>
+        <v>-5.4722</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.0761</v>
+        <v>-6.4863</v>
       </c>
       <c r="F24" t="n">
-        <v>0.834</v>
+        <v>1.0141</v>
       </c>
       <c r="G24" t="n">
         <v>-5.8839</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2706</v>
+        <v>0.4993</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8883</v>
+        <v>-0.2985</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6177</v>
+        <v>0.7978</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.6882</v>
+        <v>15.2611</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4828000000000001</v>
+        <v>0.482800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>13.2056</v>
+        <v>14.7783</v>
       </c>
       <c r="G25" t="n">
         <v>10.8492</v>
       </c>
       <c r="H25" t="n">
-        <v>6.3985</v>
+        <v>6.398500000000002</v>
       </c>
       <c r="I25" t="n">
         <v>4.450400000000002</v>
@@ -2383,16 +2383,16 @@
         <v>4.9558</v>
       </c>
       <c r="L25" t="n">
-        <v>5.285799999999997</v>
+        <v>5.285799999999998</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6073999999999999</v>
+        <v>0.6073999999999997</v>
       </c>
       <c r="N25" t="n">
         <v>1.4427</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8354000000000001</v>
+        <v>-0.8354</v>
       </c>
       <c r="P25" t="n">
         <v>-2.3195</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3749</v>
+        <v>2.948</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.01769999999999972</v>
+        <v>-0.0176</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3929</v>
+        <v>2.9654</v>
       </c>
       <c r="V25" t="n">
         <v>3.7838</v>
